--- a/.proof-os/tasks/T-MEERA-CREATOR-PHASE-B/finance/meera-credit-sheet.xlsx
+++ b/.proof-os/tasks/T-MEERA-CREATOR-PHASE-B/finance/meera-credit-sheet.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OptionB" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OptionC" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan999" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;Rs.&quot;0"/>
@@ -35,6 +36,7 @@
     <numFmt numFmtId="173" formatCode="&quot;$&quot;0.000000"/>
     <numFmt numFmtId="174" formatCode="0.0000&quot; INR&quot;"/>
     <numFmt numFmtId="175" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -115,6 +117,9 @@
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1191,6 +1196,479 @@
       <c r="B84">
         <f>B9</f>
         <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>Plan999 — Rs 999/mo creator subscription: 100 credits + 5 discovery searches + 100 outreach emails w/ follow-ups (added 2026-09-04, Rohan CFO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash pricing — source: influora-ai/app/costs/pricing.py PRICING_TABLE (already used for site-verification classify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gemini input $/MTok</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Gemini output $/MTok</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Perplexity Sonar pricing — source: Perplexity API pricing (aggregator-confirmed), verified 2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sonar input $/MTok</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sonar output $/MTok</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sonar per-request fee, low search-context tier ($ / 1000 requests)</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Discovery run composition — Phase E SPEC.md §5.2, site-verification cap per Priya correction #25 (5, not 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>First-stage Perplexity calls — low end</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>First-stage Perplexity calls — high end</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Second-stage contact-query Perplexity calls, per top candidate</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Top candidates carried to second stage</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Perplexity call — input tokens (system + query)</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Perplexity call — output tokens</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Site verifications via Gemini classify (capped)</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gemini classify — input tokens (scraped page text)</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gemini classify — output tokens</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Claude fit-scoring call — input tokens (Sonnet)</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Claude fit-scoring call — output tokens (Sonnet)</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Outreach email composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Mailgun Foundation plan — USD/month, source: mailgun.com pricing, verified 2026-09-04</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Mailgun Foundation plan — included messages/month</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Pitch draft — Claude Sonnet input tokens</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Pitch draft — Claude Sonnet output tokens</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Follow-up draft — Claude Haiku input tokens</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Follow-up draft — Claude Haiku output tokens</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Max follow-ups per pitch (plan text)</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Plan999 price and GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>List price INR/month</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>GST rate (=Assumptions!B53)</t>
+        </is>
+      </c>
+      <c r="B121">
+        <f>B53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Deal-fee sensitivity: platform fee on one extra Rs 5,000 deal/month (=B46*B45)</t>
+        </is>
+      </c>
+      <c r="B123">
+        <f>B46*B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Plan999 usage personas (per creator per month) — distinct from the Option B/C personas above</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Turns</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Replies-&gt;briefs</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Searches</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Pitches</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Follow-ups</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Email-count reading used</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>20</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" t="n">
+        <v>20</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>20 pitches, 0 follow-ups (task gives no follow-up count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Typical</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>60</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>10</v>
+      </c>
+      <c r="E128" t="n">
+        <v>5</v>
+      </c>
+      <c r="F128" t="n">
+        <v>34</v>
+      </c>
+      <c r="G128" t="n">
+        <v>66</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Interp. B: "100 emails" = 100 total sends incl. follow-ups</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>100</v>
+      </c>
+      <c r="C129" t="n">
+        <v>20</v>
+      </c>
+      <c r="D129" t="n">
+        <v>25</v>
+      </c>
+      <c r="E129" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" t="n">
+        <v>100</v>
+      </c>
+      <c r="G129" t="n">
+        <v>200</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Interp. A: task states "100 emails plus 200 follow-ups" explicitly</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Max abuse</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>100</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" t="n">
+        <v>100</v>
+      </c>
+      <c r="G130" t="n">
+        <v>200</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Every included unit maxed; worst-case (Interp. A) email reading</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3522,4 +4000,746 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Plan999 - Rs 999/mo creator plan (100 credits + 5 discovery searches + 100 outreach emails w/ follow-ups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Recomputed 2026-09-04 by Rohan (CFO). Every cell below is a formula off Assumptions/UnitCosts - nothing here is pasted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>1. Discovery run - recomputed unit cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Perplexity cost per call, $ (tokens + per-request fee)</t>
+        </is>
+      </c>
+      <c r="B5" s="14">
+        <f>(Assumptions!B102*Assumptions!B93+Assumptions!B103*Assumptions!B94)/1000000+Assumptions!B95/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>First-stage calls (low..high)</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>Assumptions!B98</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>Assumptions!B99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Second-stage contact calls (top5 x 2)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>Assumptions!B100*Assumptions!B101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Perplexity calls (low..high)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>B6+B7</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>C6+B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Perplexity cost, $ (low..high)</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
+        <f>B8*B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="14">
+        <f>C8*B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gemini classify cost per site, $</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>(Assumptions!B105*Assumptions!B89+Assumptions!B106*Assumptions!B90)/1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Site verifications (capped)</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>Assumptions!B104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gemini total cost, $</t>
+        </is>
+      </c>
+      <c r="B12" s="14">
+        <f>B10*B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Claude fit-scoring cost, $ (one Sonnet call)</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>Assumptions!B107*UnitCosts!B5+Assumptions!B108*UnitCosts!C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Discovery run total, $ (low..high)</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <f>B9+B12+B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="14">
+        <f>C9+B12+B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Discovery run total, INR (low..high)</t>
+        </is>
+      </c>
+      <c r="B15" s="23">
+        <f>B14*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="C15" s="23">
+        <f>C14*Assumptions!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Discovery run total, INR (midpoint, used elsewhere on this sheet)</t>
+        </is>
+      </c>
+      <c r="B16" s="23">
+        <f>AVERAGE(B15,C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Reference only - SPEC.md 11 Cost Q&amp;A pre-recompute estimate was Rs 25-40/run, sized for 12 site analyses; this sheet uses the Priya-corrected cap of 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2. Outreach email - recomputed unit cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mailgun cost per message, $ (Foundation plan amortised)</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
+        <f>Assumptions!B111/Assumptions!B112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pitch draft cost, $ (1 Sonnet call)</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <f>Assumptions!B113*UnitCosts!B5+Assumptions!B114*UnitCosts!C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Follow-up draft cost, $ (1 Haiku call)</t>
+        </is>
+      </c>
+      <c r="B22" s="14">
+        <f>Assumptions!B115*UnitCosts!B6+Assumptions!B116*UnitCosts!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>One pitch + 2 follow-ups: draft cost, $</t>
+        </is>
+      </c>
+      <c r="B23" s="14">
+        <f>B21+Assumptions!B117*B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>One pitch + 2 follow-ups: Mailgun send cost, $ (3 messages)</t>
+        </is>
+      </c>
+      <c r="B24" s="14">
+        <f>(1+Assumptions!B117)*B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>One pitch + 2 follow-ups: total, $ / INR</t>
+        </is>
+      </c>
+      <c r="B25" s="15">
+        <f>B23+B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="23">
+        <f>B25*Assumptions!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>If the pitch gets a reply that becomes a brief, add one Haiku brief extraction (INR)</t>
+        </is>
+      </c>
+      <c r="B26" s="14">
+        <f>UnitCosts!B22</f>
+        <v/>
+      </c>
+      <c r="C26" s="24">
+        <f>UnitCosts!B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>3. "100 outreach emails" - two readings of the plan text</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Reading A: 100 pitches + 200 follow-ups (100 is the pitch count, follow-ups extra)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pitches</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Follow-ups</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sends</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cost, INR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>100</v>
+      </c>
+      <c r="C30" t="n">
+        <v>200</v>
+      </c>
+      <c r="D30">
+        <f>B30+C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>(B30*B21+C30*B22+D30*B20)*Assumptions!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Reading B: 100 total sends incl. follow-ups (~34 pitches + 66 follow-ups at 2/pitch)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>34</v>
+      </c>
+      <c r="C31" t="n">
+        <v>66</v>
+      </c>
+      <c r="D31">
+        <f>B31+C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="24">
+        <f>(B31*B21+C31*B22+D31*B20)*Assumptions!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Plan text says "100 outreach emails with follow-ups per month" - the 100 reads as the total count including follow-ups (Reading B), not 100 pitches plus follow-ups on top (Reading A). Reading A costs about 3x Reading B; this ambiguity is commercially material and should be fixed in the plan copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>4. Persona cost and margin under Rs 999/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Turn cost INR</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Voice cost INR</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Brief-extract INR</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>Search cost INR</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>Email cost INR</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>Total cost INR</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>Net rev INR (GST-incl.)</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>Margin (incl.)</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>Net rev INR (GST-excl.)</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>Margin (excl.)</t>
+        </is>
+      </c>
+      <c r="L35" s="17" t="inlineStr">
+        <is>
+          <t>Net rev + Rs750 deal (incl.)</t>
+        </is>
+      </c>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>Margin +deal (incl.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <f>Assumptions!A127</f>
+        <v/>
+      </c>
+      <c r="B36" s="24">
+        <f>Assumptions!B127*UnitCosts!$B$19</f>
+        <v/>
+      </c>
+      <c r="C36" s="24">
+        <f>Assumptions!C127*UnitCosts!$B$29</f>
+        <v/>
+      </c>
+      <c r="D36" s="24">
+        <f>Assumptions!D127*UnitCosts!$B$23</f>
+        <v/>
+      </c>
+      <c r="E36" s="24">
+        <f>Assumptions!E127*$B$16</f>
+        <v/>
+      </c>
+      <c r="F36" s="24">
+        <f>(Assumptions!F127*$B$21+Assumptions!G127*$B$22+(Assumptions!F127+Assumptions!G127)*$B$20)*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G36" s="23">
+        <f>B36+C36+D36+E36+F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="24">
+        <f>Assumptions!$B$120/(1+Assumptions!$B$121)</f>
+        <v/>
+      </c>
+      <c r="I36" s="9">
+        <f>(H36-G36)/H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="24">
+        <f>Assumptions!$B$120</f>
+        <v/>
+      </c>
+      <c r="K36" s="9">
+        <f>(J36-G36)/J36</f>
+        <v/>
+      </c>
+      <c r="L36" s="24">
+        <f>H36+Assumptions!$B$123</f>
+        <v/>
+      </c>
+      <c r="M36" s="9">
+        <f>(L36-G36)/L36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <f>Assumptions!A128</f>
+        <v/>
+      </c>
+      <c r="B37" s="24">
+        <f>Assumptions!B128*UnitCosts!$B$19</f>
+        <v/>
+      </c>
+      <c r="C37" s="24">
+        <f>Assumptions!C128*UnitCosts!$B$29</f>
+        <v/>
+      </c>
+      <c r="D37" s="24">
+        <f>Assumptions!D128*UnitCosts!$B$23</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>Assumptions!E128*$B$16</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>(Assumptions!F128*$B$21+Assumptions!G128*$B$22+(Assumptions!F128+Assumptions!G128)*$B$20)*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G37" s="23">
+        <f>B37+C37+D37+E37+F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="24">
+        <f>Assumptions!$B$120/(1+Assumptions!$B$121)</f>
+        <v/>
+      </c>
+      <c r="I37" s="9">
+        <f>(H37-G37)/H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="24">
+        <f>Assumptions!$B$120</f>
+        <v/>
+      </c>
+      <c r="K37" s="9">
+        <f>(J37-G37)/J37</f>
+        <v/>
+      </c>
+      <c r="L37" s="24">
+        <f>H37+Assumptions!$B$123</f>
+        <v/>
+      </c>
+      <c r="M37" s="9">
+        <f>(L37-G37)/L37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <f>Assumptions!A129</f>
+        <v/>
+      </c>
+      <c r="B38" s="24">
+        <f>Assumptions!B129*UnitCosts!$B$19</f>
+        <v/>
+      </c>
+      <c r="C38" s="24">
+        <f>Assumptions!C129*UnitCosts!$B$29</f>
+        <v/>
+      </c>
+      <c r="D38" s="24">
+        <f>Assumptions!D129*UnitCosts!$B$23</f>
+        <v/>
+      </c>
+      <c r="E38" s="24">
+        <f>Assumptions!E129*$B$16</f>
+        <v/>
+      </c>
+      <c r="F38" s="24">
+        <f>(Assumptions!F129*$B$21+Assumptions!G129*$B$22+(Assumptions!F129+Assumptions!G129)*$B$20)*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G38" s="23">
+        <f>B38+C38+D38+E38+F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="24">
+        <f>Assumptions!$B$120/(1+Assumptions!$B$121)</f>
+        <v/>
+      </c>
+      <c r="I38" s="9">
+        <f>(H38-G38)/H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="24">
+        <f>Assumptions!$B$120</f>
+        <v/>
+      </c>
+      <c r="K38" s="9">
+        <f>(J38-G38)/J38</f>
+        <v/>
+      </c>
+      <c r="L38" s="24">
+        <f>H38+Assumptions!$B$123</f>
+        <v/>
+      </c>
+      <c r="M38" s="9">
+        <f>(L38-G38)/L38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <f>Assumptions!A130</f>
+        <v/>
+      </c>
+      <c r="B39" s="24">
+        <f>Assumptions!B130*UnitCosts!$B$19</f>
+        <v/>
+      </c>
+      <c r="C39" s="24">
+        <f>Assumptions!C130*UnitCosts!$B$29</f>
+        <v/>
+      </c>
+      <c r="D39" s="24">
+        <f>Assumptions!D130*UnitCosts!$B$23</f>
+        <v/>
+      </c>
+      <c r="E39" s="24">
+        <f>Assumptions!E130*$B$16</f>
+        <v/>
+      </c>
+      <c r="F39" s="24">
+        <f>(Assumptions!F130*$B$21+Assumptions!G130*$B$22+(Assumptions!F130+Assumptions!G130)*$B$20)*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G39" s="23">
+        <f>B39+C39+D39+E39+F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="24">
+        <f>Assumptions!$B$120/(1+Assumptions!$B$121)</f>
+        <v/>
+      </c>
+      <c r="I39" s="9">
+        <f>(H39-G39)/H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="24">
+        <f>Assumptions!$B$120</f>
+        <v/>
+      </c>
+      <c r="K39" s="9">
+        <f>(J39-G39)/J39</f>
+        <v/>
+      </c>
+      <c r="L39" s="24">
+        <f>H39+Assumptions!$B$123</f>
+        <v/>
+      </c>
+      <c r="M39" s="9">
+        <f>(L39-G39)/L39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Credit-pool check: Heavy needs 100 turn-credits + 40 voice-credits (20 voice x 2cr) = 140 credits vs 100 included - Heavy structurally exceeds the credit pool before counting searches/emails (which sit outside the pool by plan design). Max abuse is defined here as pure turns (100 credits, exactly the pool) so it does not breach the pool by itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>5. Break-even at Typical usage - searches/emails before margin &lt; 60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Typical fixed cost (turns+briefs), INR</t>
+        </is>
+      </c>
+      <c r="B44" s="24">
+        <f>B37+D37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Net revenue basis (GST-inclusive), INR</t>
+        </is>
+      </c>
+      <c r="B45" s="24">
+        <f>H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cost budget at 60% margin (40% of revenue), INR</t>
+        </is>
+      </c>
+      <c r="B46" s="24">
+        <f>0.4*B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Variable (search+email) budget remaining, INR</t>
+        </is>
+      </c>
+      <c r="B47" s="24">
+        <f>B46-B44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Max discovery searches/month if emails held at 100 (Reading B cost)</t>
+        </is>
+      </c>
+      <c r="B48" s="25">
+        <f>(B47-E31)/$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Max "100-email" blocks/month if searches held at 5</t>
+        </is>
+      </c>
+      <c r="B49" s="25">
+        <f>(B47-5*$B$16)/E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Reading: at Typical load, cost headroom to 60% margin is wide on searches/emails - roughly 20+ searches or about 4x the email allowance - because Perplexity/Mailgun/Haiku unit costs are all sub-rupee to a few rupees each. The real margin risk is turn+voice credit intensity (Heavy/Max abuse rows above), not search or email volume.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>